--- a/Documents/Original/FlexChroma_Brim_info.xlsx
+++ b/Documents/Original/FlexChroma_Brim_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j0814240\Documents\F-C\Git\FlexChroma\Documents\Original\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DA7CDA-6BED-448F-9011-253232F6FE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE207FEB-6F43-4081-8341-BA44C0AADD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3555" yWindow="2970" windowWidth="22185" windowHeight="12615" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5010" yWindow="2235" windowWidth="22185" windowHeight="12615" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Brim" sheetId="13" r:id="rId1"/>
@@ -7952,16 +7952,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>54428</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>176892</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>313168</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>83387</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>435632</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>69779</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7984,7 +7984,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12981214" y="3360964"/>
+          <a:off x="3578678" y="4231821"/>
           <a:ext cx="11144454" cy="3798137"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/Documents/Original/FlexChroma_Brim_info.xlsx
+++ b/Documents/Original/FlexChroma_Brim_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j0814240\Documents\F-C\Git\FlexChroma\Documents\Original\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FlexChroma\Documents\Original\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE207FEB-6F43-4081-8341-BA44C0AADD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D40808-43E0-4FF5-990A-526EED5D3FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="2235" windowWidth="22185" windowHeight="12615" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Brim" sheetId="13" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="129">
   <si>
     <t>Line</t>
     <phoneticPr fontId="1"/>
@@ -241,10 +241,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3letters</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Neu</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -302,10 +298,6 @@
   </si>
   <si>
     <t>Line name</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2 letters</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -505,6 +497,50 @@
     <t>S4b</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>Blend Color Checker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ex. STD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Standard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Detail</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DTL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tools</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>T1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Prec</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hint</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -576,7 +612,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="91">
+  <borders count="97">
     <border>
       <left/>
       <right/>
@@ -1123,36 +1159,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -1195,32 +1201,6 @@
       </left>
       <right/>
       <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="hair">
@@ -1430,19 +1410,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -1458,17 +1425,6 @@
         <color auto="1"/>
       </left>
       <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top/>
@@ -1750,6 +1706,172 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1757,7 +1879,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -1765,187 +1887,43 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="77" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="56" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="57" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="60" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="73" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="82" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="83" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="61" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="62" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="65" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="60" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="66" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="84" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1978,6 +1956,21 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1987,13 +1980,70 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="69" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="70" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="62" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="65" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="66" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="71" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2002,52 +2052,127 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="72" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="73" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="69" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="61" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="57" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="57" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="56" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="60" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="73" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="75" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="76" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="77" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="80" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="80" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="82" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="61" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="83" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="84" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="85" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2057,13 +2182,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="87" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="65" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="88" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2072,6 +2191,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="90" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="91" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="92" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="93" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="94" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="95" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="96" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2112,13 +2249,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>103908</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>80530</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1229591</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>90921</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2180,13 +2317,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>166169</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>552449</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2248,13 +2385,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2303,6 +2440,133 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="10" name="グループ化 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73AFDB20-4443-B1CD-A84A-76A0FF230175}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6225540" y="12793980"/>
+          <a:ext cx="4739640" cy="2712720"/>
+          <a:chOff x="6225540" y="12793980"/>
+          <a:chExt cx="4739640" cy="2712720"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="7" name="図 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2499DB3-8C2E-3AA8-AC89-6205ACE43E12}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="8823960" y="12793980"/>
+            <a:ext cx="2141220" cy="2712720"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:extLst>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="9" name="図 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{279D2115-7C27-10E6-7E39-F64261D1F9CB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="6225540" y="12793980"/>
+            <a:ext cx="2529840" cy="1112520"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:extLst>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2397,8 +2661,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5102087" y="6891130"/>
-          <a:ext cx="6069081" cy="1818034"/>
+          <a:off x="4598504" y="6722165"/>
+          <a:ext cx="5467764" cy="1773308"/>
           <a:chOff x="4240696" y="5938629"/>
           <a:chExt cx="6069081" cy="1818034"/>
         </a:xfrm>
@@ -2570,8 +2834,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3260982" y="9679411"/>
-          <a:ext cx="5957562" cy="2522113"/>
+          <a:off x="2946243" y="9442529"/>
+          <a:ext cx="5381092" cy="2457508"/>
           <a:chOff x="3260982" y="9679411"/>
           <a:chExt cx="5957562" cy="2522113"/>
         </a:xfrm>
@@ -2702,8 +2966,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1504207" y="1510392"/>
-          <a:ext cx="11136829" cy="3703382"/>
+          <a:off x="1362693" y="1401535"/>
+          <a:ext cx="10004714" cy="3417632"/>
           <a:chOff x="1504207" y="1551214"/>
           <a:chExt cx="11136829" cy="3703382"/>
         </a:xfrm>
@@ -8282,21 +8546,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64526695-9BCB-44A9-9A34-911DAE368A41}">
-  <dimension ref="A1:H174"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:H184"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="2.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.109375" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8306,7 +8570,7 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -8318,477 +8582,499 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="66" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="66" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="72"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="73"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="74"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="26" t="s">
+      <c r="D5" s="31"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="37" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
-      <c r="B6" s="53"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="44"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="38"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
-      <c r="B7" s="53"/>
-      <c r="C7" s="20" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="75"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="20" t="s">
+      <c r="D7" s="32"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="44" t="s">
+      <c r="G7" s="38" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="58"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="34"/>
+      <c r="F9" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="35"/>
+      <c r="F11" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C13" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D13" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="56" t="s">
+      <c r="E13" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F13" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G13" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="2"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="20" t="s">
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D15" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="E15" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F15" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="44" t="s">
+      <c r="G15" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2"/>
-      <c r="B13" s="52" t="s">
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="31"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="51"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="32"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="55"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C21" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D21" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="61"/>
-      <c r="F13" s="26" t="s">
+      <c r="E21" s="35"/>
+      <c r="F21" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="G13" s="43" t="s">
+      <c r="G21" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="2"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="2"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="20" t="s">
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D23" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="20" t="s">
+      <c r="E23" s="35"/>
+      <c r="F23" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="44" t="s">
+      <c r="G23" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="2"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="2"/>
-      <c r="B17" s="52" t="s">
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C25" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="55" t="s">
+      <c r="D25" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="56" t="s">
+      <c r="E25" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F25" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="G17" s="43" t="s">
+      <c r="G25" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="2"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="2"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="20" t="s">
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="D27" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="47" t="s">
+      <c r="E27" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F27" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="44" t="s">
+      <c r="G27" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="2"/>
-      <c r="B20" s="57"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="2"/>
-      <c r="B21" s="52" t="s">
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C29" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="55" t="s">
+      <c r="D29" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="E29" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F29" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="G21" s="43" t="s">
+      <c r="G29" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="2"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="2"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="20" t="s">
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="2"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D31" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E31" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F31" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="G23" s="44" t="s">
+      <c r="G31" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="2"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="2"/>
-      <c r="B25" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="55" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="2"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="2"/>
-      <c r="B27" s="53"/>
-      <c r="C27" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="40"/>
-      <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="40"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="39"/>
       <c r="G32" s="40"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="2"/>
+      <c r="B33" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>12</v>
+      </c>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="2"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="38"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="2"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" s="38" t="s">
+        <v>24</v>
+      </c>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="67"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -8798,439 +9084,407 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
-      <c r="B38" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>51</v>
-      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
+      <c r="F38" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="G38" s="62"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="13"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="62"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
-      <c r="B40" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>53</v>
-      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="6"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="63" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
+      <c r="F41" s="64"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
-      <c r="B42" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>75</v>
-      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" s="63"/>
+      <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
+      <c r="F42" s="64"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="6"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
-      <c r="B44" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>74</v>
-      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="6"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
-      <c r="B46" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C46" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>52</v>
+      <c r="B46" s="100" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="65" t="s">
+        <v>89</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
+      <c r="G46" s="92" t="s">
+        <v>50</v>
+      </c>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="6"/>
+      <c r="B47" s="101"/>
+      <c r="C47" s="40"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
+      <c r="G47" s="39"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
-      <c r="B48" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C48" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>54</v>
+      <c r="B48" s="102" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="38" t="s">
+        <v>52</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
+      <c r="G48" s="30" t="s">
+        <v>37</v>
+      </c>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="30"/>
+      <c r="B49" s="102"/>
+      <c r="C49" s="38"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
+      <c r="G49" s="30"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
-      <c r="B50" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C50" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" s="38" t="s">
-        <v>55</v>
+      <c r="B50" s="102" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" s="38" t="s">
+        <v>73</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
+      <c r="G50" s="30" t="s">
+        <v>74</v>
+      </c>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
-      <c r="B51" s="35"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="39"/>
+      <c r="B51" s="102"/>
+      <c r="C51" s="38"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
+      <c r="G51" s="30"/>
       <c r="H51" s="2"/>
     </row>
-    <row r="52" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
-      <c r="B52" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C52" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D52" s="27" t="s">
-        <v>56</v>
+      <c r="B52" s="102" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="38" t="s">
+        <v>72</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
+      <c r="G52" s="30" t="s">
+        <v>71</v>
+      </c>
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
-      <c r="B53" s="24"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="28"/>
+      <c r="B53" s="102"/>
+      <c r="C53" s="38"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
+      <c r="G53" s="30"/>
       <c r="H53" s="2"/>
     </row>
-    <row r="54" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
-      <c r="B54" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C54" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>57</v>
+      <c r="B54" s="103" t="s">
+        <v>36</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>51</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
+      <c r="G54" s="60" t="s">
+        <v>40</v>
+      </c>
       <c r="H54" s="2"/>
     </row>
-    <row r="55" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="6"/>
+      <c r="B55" s="102"/>
+      <c r="C55" s="38"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
+      <c r="G55" s="30"/>
       <c r="H55" s="2"/>
     </row>
-    <row r="56" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
-      <c r="B56" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>58</v>
+      <c r="B56" s="97" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" s="55" t="s">
+        <v>53</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
+      <c r="G56" s="96" t="s">
+        <v>41</v>
+      </c>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="6"/>
+      <c r="B57" s="103"/>
+      <c r="C57" s="53"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
+      <c r="G57" s="60"/>
       <c r="H57" s="2"/>
     </row>
-    <row r="58" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>55</v>
+      <c r="C58" s="75" t="s">
+        <v>54</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
+      <c r="G58" s="93" t="s">
+        <v>39</v>
+      </c>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="6"/>
+      <c r="B59" s="105"/>
+      <c r="C59" s="25"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
+      <c r="G59" s="94"/>
       <c r="H59" s="2"/>
     </row>
-    <row r="60" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
-      <c r="B60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C60" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>48</v>
+      <c r="B60" s="106" t="s">
+        <v>42</v>
+      </c>
+      <c r="C60" s="99" t="s">
+        <v>55</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
+      <c r="G60" s="95" t="s">
+        <v>42</v>
+      </c>
       <c r="H60" s="2"/>
     </row>
-    <row r="61" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="19"/>
+      <c r="B61" s="107"/>
+      <c r="C61" s="37"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
+      <c r="G61" s="29"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="B62" s="102" t="s">
+        <v>43</v>
+      </c>
+      <c r="C62" s="38" t="s">
+        <v>56</v>
+      </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
+      <c r="G62" s="30" t="s">
+        <v>46</v>
+      </c>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
+      <c r="B63" s="102"/>
+      <c r="C63" s="38"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
+      <c r="G63" s="30"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
-      <c r="B64" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C64" s="16"/>
-      <c r="D64" s="2"/>
+      <c r="B64" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64" s="38" t="s">
+        <v>57</v>
+      </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
+      <c r="G64" s="30" t="s">
+        <v>47</v>
+      </c>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="2"/>
+      <c r="B65" s="102"/>
+      <c r="C65" s="38"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
+      <c r="G65" s="30"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
-      <c r="B66" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D66" s="2"/>
+      <c r="B66" s="102" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" s="38" t="s">
+        <v>54</v>
+      </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
+      <c r="G66" s="30" t="s">
+        <v>39</v>
+      </c>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="2"/>
+      <c r="B67" s="102"/>
+      <c r="C67" s="38"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
+      <c r="G67" s="30"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
-      <c r="B68" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C68" s="6">
-        <v>1</v>
-      </c>
-      <c r="D68" s="2"/>
+      <c r="B68" s="102" t="s">
+        <v>45</v>
+      </c>
+      <c r="C68" s="38" t="s">
+        <v>48</v>
+      </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
+      <c r="G68" s="30" t="s">
+        <v>49</v>
+      </c>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="2"/>
+      <c r="B69" s="108"/>
+      <c r="C69" s="67"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
+      <c r="G69" s="49"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
-      <c r="B70" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C70" s="6">
-        <v>2</v>
-      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="6"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
-      <c r="B72" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C72" s="13">
-        <v>4</v>
+      <c r="B72" s="77" t="s">
+        <v>59</v>
+      </c>
+      <c r="C72" s="79" t="s">
+        <v>89</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
@@ -9238,43 +9492,47 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="14"/>
+      <c r="B73" s="78"/>
+      <c r="C73" s="80"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
+      <c r="B74" s="81" t="s">
+        <v>60</v>
+      </c>
+      <c r="C74" s="82" t="s">
+        <v>64</v>
+      </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="6"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
-      <c r="B76" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>67</v>
+      <c r="B76" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C76" s="6">
+        <v>1</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
@@ -9282,23 +9540,23 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="13"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="6"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
-      <c r="B78" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C78" s="18" t="s">
-        <v>28</v>
+      <c r="B78" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C78" s="6">
+        <v>2</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
@@ -9306,9 +9564,9 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
     </row>
-    <row r="79" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
-      <c r="B79" s="5"/>
+      <c r="B79" s="4"/>
       <c r="C79" s="6"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
@@ -9316,13 +9574,13 @@
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
     </row>
-    <row r="80" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
-      <c r="B80" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>29</v>
+      <c r="B80" s="78" t="s">
+        <v>63</v>
+      </c>
+      <c r="C80" s="80">
+        <v>4</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -9330,47 +9588,45 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
     </row>
-    <row r="81" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="6"/>
+      <c r="B81" s="83"/>
+      <c r="C81" s="84"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
     </row>
-    <row r="82" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
-      <c r="B82" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="6"/>
+      <c r="B83" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
-      <c r="B84" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>34</v>
+      <c r="B84" s="77" t="s">
+        <v>65</v>
+      </c>
+      <c r="C84" s="79" t="s">
+        <v>89</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
@@ -9378,23 +9634,23 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="6"/>
+      <c r="B85" s="78"/>
+      <c r="C85" s="80"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
-      <c r="B86" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>30</v>
+      <c r="B86" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="C86" s="82" t="s">
+        <v>28</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
@@ -9402,9 +9658,9 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
-      <c r="B87" s="5"/>
+      <c r="B87" s="4"/>
       <c r="C87" s="6"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
@@ -9412,13 +9668,13 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
-      <c r="B88" s="5" t="s">
-        <v>78</v>
+      <c r="B88" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
@@ -9426,9 +9682,9 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
     </row>
-    <row r="89" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
-      <c r="B89" s="5"/>
+      <c r="B89" s="4"/>
       <c r="C89" s="6"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
@@ -9436,13 +9692,13 @@
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
     </row>
-    <row r="90" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
-      <c r="B90" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C90" s="9" t="s">
-        <v>81</v>
+      <c r="B90" s="97" t="s">
+        <v>90</v>
+      </c>
+      <c r="C90" s="88" t="s">
+        <v>127</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
@@ -9450,117 +9706,137 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
     </row>
-    <row r="91" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
-      <c r="B91" s="8"/>
-      <c r="C91" s="10"/>
+      <c r="B91" s="98"/>
+      <c r="C91" s="89"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
     </row>
-    <row r="92" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
+      <c r="B92" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="C92" s="90" t="s">
+        <v>33</v>
+      </c>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
     </row>
-    <row r="93" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="6"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
     </row>
-    <row r="94" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
+      <c r="B94" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
     </row>
-    <row r="95" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="6"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
     </row>
-    <row r="96" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
+      <c r="B96" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="6"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
     </row>
-    <row r="98" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
+      <c r="B98" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="6"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
+      <c r="B100" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="C100" s="88" t="s">
+        <v>79</v>
+      </c>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
+      <c r="B101" s="98"/>
+      <c r="C101" s="89"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -9570,7 +9846,7 @@
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -9580,67 +9856,79 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
+      <c r="B104" s="77" t="s">
+        <v>119</v>
+      </c>
+      <c r="C104" s="79" t="s">
+        <v>89</v>
+      </c>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
+      <c r="B105" s="78"/>
+      <c r="C105" s="80"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
+      <c r="B106" s="81" t="s">
+        <v>121</v>
+      </c>
+      <c r="C106" s="82" t="s">
+        <v>123</v>
+      </c>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="6"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
+      <c r="B108" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
     </row>
-    <row r="109" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
+      <c r="B109" s="7"/>
+      <c r="C109" s="9"/>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
     </row>
-    <row r="110" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -9650,7 +9938,7 @@
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
     </row>
-    <row r="111" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -9660,9 +9948,11 @@
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
     </row>
-    <row r="112" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
+      <c r="B112" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
@@ -9670,227 +9960,251 @@
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
     </row>
-    <row r="113" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
+      <c r="B113" s="110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" s="79" t="s">
+        <v>89</v>
+      </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
+      <c r="B114" s="105"/>
+      <c r="C114" s="80"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
+      <c r="B115" s="109" t="s">
+        <v>100</v>
+      </c>
+      <c r="C115" s="82" t="s">
+        <v>109</v>
+      </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
+      <c r="B116" s="103"/>
+      <c r="C116" s="6"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
     </row>
-    <row r="117" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
+      <c r="B117" s="97" t="s">
+        <v>101</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
+      <c r="B118" s="103"/>
+      <c r="C118" s="6"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
+      <c r="B119" s="97" t="s">
+        <v>102</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>110</v>
+      </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
+      <c r="B120" s="103"/>
+      <c r="C120" s="6"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
+      <c r="B121" s="97" t="s">
+        <v>103</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
-      <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
+      <c r="B122" s="103"/>
+      <c r="C122" s="6"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
+      <c r="B123" s="97" t="s">
+        <v>104</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>113</v>
+      </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
+      <c r="B124" s="103"/>
+      <c r="C124" s="6"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
+      <c r="B125" s="97" t="s">
+        <v>105</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
+      <c r="B126" s="103"/>
+      <c r="C126" s="6"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
+      <c r="B127" s="97" t="s">
+        <v>106</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
+      <c r="B128" s="103"/>
+      <c r="C128" s="6"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
+      <c r="B129" s="97" t="s">
+        <v>107</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
-      <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
+      <c r="B130" s="103"/>
+      <c r="C130" s="6"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
+      <c r="B131" s="97" t="s">
+        <v>125</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>126</v>
+      </c>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
+      <c r="B132" s="103"/>
+      <c r="C132" s="6"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
+      <c r="B133" s="97" t="s">
+        <v>108</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>117</v>
+      </c>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
-      <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
+      <c r="B134" s="98"/>
+      <c r="C134" s="9"/>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -9900,7 +10214,7 @@
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -9910,7 +10224,7 @@
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -9920,7 +10234,7 @@
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -9930,7 +10244,7 @@
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -9940,7 +10254,7 @@
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
     </row>
-    <row r="140" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -9950,7 +10264,7 @@
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
     </row>
-    <row r="141" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -9960,7 +10274,7 @@
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -9970,7 +10284,7 @@
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -9980,7 +10294,7 @@
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -9990,7 +10304,7 @@
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -10000,7 +10314,7 @@
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -10010,7 +10324,7 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -10020,7 +10334,7 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -10030,7 +10344,7 @@
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -10040,7 +10354,7 @@
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -10050,7 +10364,7 @@
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -10060,7 +10374,7 @@
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -10070,7 +10384,7 @@
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
     </row>
-    <row r="153" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -10080,7 +10394,7 @@
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
     </row>
-    <row r="154" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -10090,7 +10404,7 @@
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
     </row>
-    <row r="155" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -10100,7 +10414,7 @@
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
     </row>
-    <row r="156" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -10110,7 +10424,7 @@
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
     </row>
-    <row r="157" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -10120,7 +10434,7 @@
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
     </row>
-    <row r="158" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -10130,7 +10444,7 @@
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
     </row>
-    <row r="159" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -10140,7 +10454,7 @@
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
     </row>
-    <row r="160" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -10150,7 +10464,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -10160,7 +10474,7 @@
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
     </row>
-    <row r="162" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -10170,7 +10484,7 @@
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
     </row>
-    <row r="163" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -10180,7 +10494,7 @@
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
     </row>
-    <row r="164" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -10190,7 +10504,7 @@
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
     </row>
-    <row r="165" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -10200,7 +10514,7 @@
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -10210,7 +10524,7 @@
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -10220,7 +10534,7 @@
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -10230,7 +10544,7 @@
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -10240,7 +10554,7 @@
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -10250,148 +10564,295 @@
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
-    </row>
-    <row r="172" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="H171" s="2"/>
+    </row>
+    <row r="172" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
-    </row>
-    <row r="173" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="2"/>
+    </row>
+    <row r="173" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="2"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+    </row>
+    <row r="174" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+    </row>
+    <row r="175" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2"/>
+      <c r="H175" s="2"/>
+    </row>
+    <row r="176" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="2"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2"/>
+      <c r="H176" s="2"/>
+    </row>
+    <row r="177" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="2"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+    </row>
+    <row r="178" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="2"/>
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="2"/>
+    </row>
+    <row r="179" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="2"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="2"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2"/>
+      <c r="H179" s="2"/>
+    </row>
+    <row r="180" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="2"/>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="2"/>
+    </row>
+    <row r="181" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="2"/>
+    </row>
+    <row r="182" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="2"/>
+    </row>
+    <row r="183" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="132">
+  <mergeCells count="179">
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="F17:G18"/>
+    <mergeCell ref="F19:G20"/>
+    <mergeCell ref="E17:E20"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="C131:C132"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="C125:C126"/>
+    <mergeCell ref="C127:C128"/>
+    <mergeCell ref="C129:C130"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="B127:B128"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="C115:C116"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="F38:G40"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:E4"/>
     <mergeCell ref="F3:G4"/>
     <mergeCell ref="B5:B8"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D8"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E16"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B9:B12"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="F30:G32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="D11:D12"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10403,18 +10864,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D09D71-3F9C-4BDB-BCC5-2D63E9BEF5B5}">
   <dimension ref="A1:H174"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
     <col min="2" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.375" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="2.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.109375" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10424,7 +10885,7 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -10436,383 +10897,383 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="66" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="66" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="72"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="73"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="74"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="26" t="s">
+      <c r="D5" s="31"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="37" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
-      <c r="B6" s="53"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="44"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="38"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
-      <c r="B7" s="53"/>
-      <c r="C7" s="20" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="75"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="20" t="s">
+      <c r="D7" s="32"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="44" t="s">
+      <c r="G7" s="38" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="58"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="56" t="s">
+      <c r="E9" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="37" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="44"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="38"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="20" t="s">
+      <c r="B11" s="27"/>
+      <c r="C11" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D11" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="E11" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="44" t="s">
+      <c r="G11" s="38" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="58"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="40"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="77" t="s">
+      <c r="D13" s="31"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="G13" s="78"/>
+      <c r="G13" s="51"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="80"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="53"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="20" t="s">
+      <c r="B15" s="27"/>
+      <c r="C15" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="32"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="75"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="81" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="82"/>
+      <c r="G15" s="55"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="87"/>
-      <c r="G16" s="88"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="57"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
-      <c r="B17" s="83" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="84" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" s="84" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" s="29" t="s">
+      <c r="B17" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="G17" s="80" t="s">
+      <c r="G17" s="53" t="s">
         <v>12</v>
       </c>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="44"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="38"/>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="44" t="s">
-        <v>83</v>
+      <c r="B19" s="27"/>
+      <c r="C19" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>81</v>
       </c>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
-      <c r="B20" s="57"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="58"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
-      <c r="B21" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="26" t="s">
+      <c r="B21" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="G21" s="43" t="s">
+      <c r="G21" s="37" t="s">
         <v>12</v>
       </c>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="44"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="38"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>83</v>
+      <c r="B23" s="27"/>
+      <c r="C23" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>81</v>
       </c>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="58"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
-      <c r="B25" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="F25" s="26" t="s">
+      <c r="B25" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="G25" s="43" t="s">
+      <c r="G25" s="37" t="s">
         <v>12</v>
       </c>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="44"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="38"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
-      <c r="B27" s="53"/>
-      <c r="C27" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D27" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" s="44" t="s">
-        <v>83</v>
+      <c r="B27" s="27"/>
+      <c r="C27" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>81</v>
       </c>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="49"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="67"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -10822,67 +11283,67 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="40"/>
+      <c r="C30" s="62"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="40"/>
+      <c r="C31" s="62"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="62"/>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="40"/>
+      <c r="C32" s="62"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="41"/>
+      <c r="C33" s="63"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="42"/>
+      <c r="F33" s="64"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="41"/>
+      <c r="C34" s="63"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="42"/>
+      <c r="F34" s="64"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="3"/>
+      <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="3"/>
+      <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -10892,102 +11353,102 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
-      <c r="B38" s="64" t="s">
+      <c r="B38" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="90" t="s">
-        <v>91</v>
+      <c r="C38" s="65" t="s">
+        <v>89</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="100" t="s">
+      <c r="E38" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F38" s="103" t="s">
-        <v>99</v>
+      <c r="F38" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
-      <c r="B39" s="65"/>
-      <c r="C39" s="58"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="40"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="101"/>
-      <c r="F39" s="104"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="14"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
-      <c r="B40" s="92" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" s="44" t="s">
-        <v>53</v>
+      <c r="B40" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="38" t="s">
+        <v>52</v>
       </c>
       <c r="D40" s="2"/>
-      <c r="E40" s="101"/>
-      <c r="F40" s="104"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="14"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
-      <c r="B41" s="92"/>
-      <c r="C41" s="44"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="38"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="102"/>
-      <c r="F41" s="105"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="15"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
-      <c r="B42" s="92" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="44" t="s">
-        <v>75</v>
+      <c r="B42" s="68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" s="38" t="s">
+        <v>73</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
-      <c r="B43" s="92"/>
-      <c r="C43" s="44"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="38"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
-      <c r="B44" s="92" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="44" t="s">
-        <v>74</v>
+      <c r="B44" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="38" t="s">
+        <v>72</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -10995,23 +11456,23 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
-      <c r="B45" s="92"/>
-      <c r="C45" s="44"/>
+      <c r="B45" s="68"/>
+      <c r="C45" s="38"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
-      <c r="B46" s="32" t="s">
+      <c r="B46" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="C46" s="80" t="s">
-        <v>52</v>
+      <c r="C46" s="53" t="s">
+        <v>51</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -11019,23 +11480,23 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
-      <c r="B47" s="92"/>
-      <c r="C47" s="44"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="38"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
-      <c r="B48" s="31" t="s">
+      <c r="B48" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="82" t="s">
-        <v>54</v>
+      <c r="C48" s="55" t="s">
+        <v>53</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -11043,23 +11504,23 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="80"/>
-      <c r="D49" s="4"/>
+      <c r="B49" s="69"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="3"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
-      <c r="B50" s="34" t="s">
+      <c r="B50" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="91" t="s">
-        <v>55</v>
+      <c r="C50" s="75" t="s">
+        <v>54</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -11067,23 +11528,23 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
-      <c r="B51" s="89"/>
-      <c r="C51" s="88"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="57"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
     </row>
-    <row r="52" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
-      <c r="B52" s="35" t="s">
+      <c r="B52" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="73" t="s">
-        <v>56</v>
+      <c r="C52" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -11091,23 +11552,23 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
-      <c r="B53" s="93"/>
-      <c r="C53" s="43"/>
+      <c r="B53" s="71"/>
+      <c r="C53" s="37"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
     </row>
-    <row r="54" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
-      <c r="B54" s="92" t="s">
+      <c r="B54" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C54" s="44" t="s">
-        <v>57</v>
+      <c r="C54" s="38" t="s">
+        <v>56</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -11115,23 +11576,23 @@
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
     </row>
-    <row r="55" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
-      <c r="B55" s="92"/>
-      <c r="C55" s="44"/>
+      <c r="B55" s="68"/>
+      <c r="C55" s="38"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
     </row>
-    <row r="56" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
-      <c r="B56" s="92" t="s">
+      <c r="B56" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="44" t="s">
-        <v>58</v>
+      <c r="C56" s="38" t="s">
+        <v>57</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
@@ -11139,23 +11600,23 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
-      <c r="B57" s="92"/>
-      <c r="C57" s="44"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="38"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
     </row>
-    <row r="58" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
-      <c r="B58" s="92" t="s">
+      <c r="B58" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="44" t="s">
-        <v>55</v>
+      <c r="C58" s="38" t="s">
+        <v>54</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -11163,22 +11624,22 @@
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
-      <c r="B59" s="92"/>
-      <c r="C59" s="44"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="38"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
     </row>
-    <row r="60" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
-      <c r="B60" s="92" t="s">
+      <c r="B60" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="44" t="s">
+      <c r="C60" s="38" t="s">
         <v>48</v>
       </c>
       <c r="D60" s="2"/>
@@ -11187,17 +11648,17 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
     </row>
-    <row r="61" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
-      <c r="B61" s="94"/>
-      <c r="C61" s="49"/>
+      <c r="B61" s="76"/>
+      <c r="C61" s="67"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -11207,10 +11668,10 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -11219,13 +11680,13 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
-      <c r="B64" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>91</v>
+      <c r="B64" s="77" t="s">
+        <v>59</v>
+      </c>
+      <c r="C64" s="79" t="s">
+        <v>89</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
@@ -11233,23 +11694,23 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="13"/>
+      <c r="B65" s="78"/>
+      <c r="C65" s="80"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
-      <c r="B66" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>88</v>
+      <c r="B66" s="81" t="s">
+        <v>60</v>
+      </c>
+      <c r="C66" s="82" t="s">
+        <v>86</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
@@ -11257,9 +11718,9 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
-      <c r="B67" s="5"/>
+      <c r="B67" s="4"/>
       <c r="C67" s="6"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
@@ -11267,13 +11728,13 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
-      <c r="B68" s="5" t="s">
-        <v>62</v>
+      <c r="B68" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
@@ -11281,9 +11742,9 @@
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
-      <c r="B69" s="5"/>
+      <c r="B69" s="4"/>
       <c r="C69" s="6"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
@@ -11291,13 +11752,13 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
-      <c r="B70" s="5" t="s">
-        <v>63</v>
+      <c r="B70" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
@@ -11305,9 +11766,9 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
-      <c r="B71" s="5"/>
+      <c r="B71" s="4"/>
       <c r="C71" s="6"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
@@ -11315,13 +11776,13 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
-      <c r="B72" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>95</v>
+      <c r="B72" s="78" t="s">
+        <v>63</v>
+      </c>
+      <c r="C72" s="80" t="s">
+        <v>93</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
@@ -11329,17 +11790,17 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="14"/>
+      <c r="B73" s="83"/>
+      <c r="C73" s="84"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -11349,10 +11810,10 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -11361,37 +11822,37 @@
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
-      <c r="B76" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C76" s="95"/>
-      <c r="D76" s="16" t="s">
-        <v>91</v>
+      <c r="B76" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="C76" s="85"/>
+      <c r="D76" s="79" t="s">
+        <v>89</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="99"/>
-      <c r="D77" s="13"/>
+      <c r="B77" s="78"/>
+      <c r="C77" s="86"/>
+      <c r="D77" s="80"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
-      <c r="B78" s="17" t="s">
+      <c r="B78" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="C78" s="98"/>
-      <c r="D78" s="18" t="s">
+      <c r="C78" s="87"/>
+      <c r="D78" s="82" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="2"/>
@@ -11399,22 +11860,22 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
     </row>
-    <row r="79" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="96"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="5"/>
       <c r="D79" s="6"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
     </row>
-    <row r="80" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C80" s="96"/>
+      <c r="C80" s="5"/>
       <c r="D80" s="6" t="s">
         <v>29</v>
       </c>
@@ -11423,47 +11884,47 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
     </row>
-    <row r="81" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="96"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="5"/>
       <c r="D81" s="6"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
     </row>
-    <row r="82" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
-      <c r="B82" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C82" s="96"/>
+      <c r="B82" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" s="5"/>
       <c r="D82" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
-      <c r="B83" s="21"/>
-      <c r="C83" s="97"/>
-      <c r="D83" s="19"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="9"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
-      <c r="B84" s="17" t="s">
+      <c r="B84" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C84" s="98"/>
-      <c r="D84" s="30" t="s">
+      <c r="C84" s="87"/>
+      <c r="D84" s="90" t="s">
         <v>33</v>
       </c>
       <c r="E84" s="2"/>
@@ -11471,22 +11932,22 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="96"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="5"/>
       <c r="D85" s="6"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C86" s="96"/>
+      <c r="C86" s="5"/>
       <c r="D86" s="6" t="s">
         <v>34</v>
       </c>
@@ -11495,22 +11956,22 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="96"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="5"/>
       <c r="D87" s="6"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C88" s="96"/>
+      <c r="C88" s="5"/>
       <c r="D88" s="6" t="s">
         <v>30</v>
       </c>
@@ -11519,59 +11980,59 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
     </row>
-    <row r="89" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="96"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="5"/>
       <c r="D89" s="6"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
     </row>
-    <row r="90" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C90" s="96"/>
+      <c r="C90" s="5"/>
       <c r="D90" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
     </row>
-    <row r="91" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="96"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="5"/>
       <c r="D91" s="6"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
     </row>
-    <row r="92" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
-      <c r="B92" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92" s="96"/>
-      <c r="D92" s="9" t="s">
-        <v>81</v>
+      <c r="B92" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C92" s="5"/>
+      <c r="D92" s="88" t="s">
+        <v>79</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
     </row>
-    <row r="93" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
-      <c r="B93" s="21"/>
-      <c r="C93" s="97"/>
-      <c r="D93" s="10"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="89"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
     </row>
-    <row r="94" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -11579,7 +12040,7 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
     </row>
-    <row r="95" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -11587,249 +12048,249 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
     </row>
-    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
     </row>
-    <row r="97" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
-      <c r="B97" s="15" t="s">
+      <c r="B97" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="C97" s="95"/>
-      <c r="D97" s="16" t="s">
-        <v>91</v>
+      <c r="C97" s="85"/>
+      <c r="D97" s="79" t="s">
+        <v>89</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
     </row>
-    <row r="98" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="99"/>
-      <c r="D98" s="13"/>
+      <c r="B98" s="78"/>
+      <c r="C98" s="86"/>
+      <c r="D98" s="80"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
     </row>
-    <row r="99" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
-      <c r="B99" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C99" s="98"/>
-      <c r="D99" s="18" t="s">
-        <v>111</v>
+      <c r="B99" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="C99" s="87"/>
+      <c r="D99" s="82" t="s">
+        <v>109</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
     </row>
-    <row r="100" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="96"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="5"/>
       <c r="D100" s="6"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
     </row>
-    <row r="101" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
-      <c r="B101" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C101" s="96"/>
+      <c r="B101" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C101" s="5"/>
       <c r="D101" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="96"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="5"/>
       <c r="D102" s="6"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
-      <c r="B103" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C103" s="96"/>
+      <c r="B103" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C103" s="5"/>
       <c r="D103" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="96"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="5"/>
       <c r="D104" s="6"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
-      <c r="B105" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C105" s="96"/>
+      <c r="B105" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C105" s="5"/>
       <c r="D105" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="96"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="5"/>
       <c r="D106" s="6"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
-      <c r="B107" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C107" s="96"/>
+      <c r="B107" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C107" s="5"/>
       <c r="D107" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="96"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="5"/>
       <c r="D108" s="6"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
     </row>
-    <row r="109" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
-      <c r="B109" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C109" s="96"/>
+      <c r="B109" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C109" s="5"/>
       <c r="D109" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
     </row>
-    <row r="110" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="96"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="5"/>
       <c r="D110" s="6"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
     </row>
-    <row r="111" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
-      <c r="B111" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C111" s="96"/>
+      <c r="B111" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C111" s="5"/>
       <c r="D111" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
     </row>
-    <row r="112" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="96"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="5"/>
       <c r="D112" s="6"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
     </row>
-    <row r="113" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
-      <c r="B113" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C113" s="96"/>
+      <c r="B113" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C113" s="5"/>
       <c r="D113" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="96"/>
+      <c r="B114" s="4"/>
+      <c r="C114" s="5"/>
       <c r="D114" s="6"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
-      <c r="B115" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C115" s="96"/>
+      <c r="B115" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C115" s="5"/>
       <c r="D115" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
-      <c r="B116" s="21"/>
-      <c r="C116" s="97"/>
-      <c r="D116" s="19"/>
+      <c r="B116" s="7"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="9"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
     </row>
-    <row r="117" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -11839,7 +12300,7 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -11849,7 +12310,7 @@
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -11859,7 +12320,7 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -11869,7 +12330,7 @@
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -11879,7 +12340,7 @@
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -11889,7 +12350,7 @@
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -11899,7 +12360,7 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -11909,7 +12370,7 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -11919,7 +12380,7 @@
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -11929,7 +12390,7 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -11939,7 +12400,7 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -11949,7 +12410,7 @@
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -11959,7 +12420,7 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -11969,7 +12430,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -11979,7 +12440,7 @@
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -11989,7 +12450,7 @@
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -11999,7 +12460,7 @@
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -12009,7 +12470,7 @@
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -12019,7 +12480,7 @@
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -12029,7 +12490,7 @@
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -12039,7 +12500,7 @@
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -12049,7 +12510,7 @@
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -12059,7 +12520,7 @@
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
     </row>
-    <row r="140" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -12069,7 +12530,7 @@
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
     </row>
-    <row r="141" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -12079,7 +12540,7 @@
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -12089,7 +12550,7 @@
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -12099,7 +12560,7 @@
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -12109,7 +12570,7 @@
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -12119,7 +12580,7 @@
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -12129,7 +12590,7 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -12139,7 +12600,7 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -12149,7 +12610,7 @@
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -12159,7 +12620,7 @@
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -12169,7 +12630,7 @@
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -12179,7 +12640,7 @@
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -12189,7 +12650,7 @@
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
     </row>
-    <row r="153" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -12199,7 +12660,7 @@
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
     </row>
-    <row r="154" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -12209,7 +12670,7 @@
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
     </row>
-    <row r="155" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -12219,7 +12680,7 @@
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
     </row>
-    <row r="156" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -12229,7 +12690,7 @@
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
     </row>
-    <row r="157" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -12239,7 +12700,7 @@
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
     </row>
-    <row r="158" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -12249,7 +12710,7 @@
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
     </row>
-    <row r="159" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -12259,7 +12720,7 @@
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
     </row>
-    <row r="160" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -12269,7 +12730,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -12279,7 +12740,7 @@
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
     </row>
-    <row r="162" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -12289,7 +12750,7 @@
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
     </row>
-    <row r="163" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -12299,7 +12760,7 @@
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
     </row>
-    <row r="164" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -12309,7 +12770,7 @@
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
     </row>
-    <row r="165" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -12319,7 +12780,7 @@
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -12329,7 +12790,7 @@
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -12339,7 +12800,7 @@
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -12349,7 +12810,7 @@
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -12359,7 +12820,7 @@
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -12369,32 +12830,117 @@
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
     </row>
-    <row r="172" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
     </row>
-    <row r="173" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="141">
-    <mergeCell ref="B111:C112"/>
-    <mergeCell ref="D111:D112"/>
-    <mergeCell ref="B113:C114"/>
-    <mergeCell ref="D113:D114"/>
-    <mergeCell ref="B115:C116"/>
-    <mergeCell ref="D115:D116"/>
-    <mergeCell ref="B101:C102"/>
-    <mergeCell ref="D101:D102"/>
-    <mergeCell ref="B103:C104"/>
-    <mergeCell ref="D103:D104"/>
-    <mergeCell ref="B105:C106"/>
-    <mergeCell ref="D105:D106"/>
-    <mergeCell ref="B107:C108"/>
-    <mergeCell ref="D107:D108"/>
-    <mergeCell ref="B109:C110"/>
-    <mergeCell ref="D109:D110"/>
+    <mergeCell ref="B82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="B97:C98"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="B99:C100"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="B84:C85"/>
+    <mergeCell ref="B86:C87"/>
+    <mergeCell ref="B88:C89"/>
+    <mergeCell ref="B90:C91"/>
+    <mergeCell ref="B92:C93"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="B76:C77"/>
+    <mergeCell ref="B78:C79"/>
+    <mergeCell ref="B80:C81"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="F30:G32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="E13:E16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="F13:G14"/>
+    <mergeCell ref="F15:G16"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
     <mergeCell ref="E38:E41"/>
     <mergeCell ref="F38:F41"/>
     <mergeCell ref="B3:B4"/>
@@ -12419,107 +12965,22 @@
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="E13:E16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="F13:G14"/>
-    <mergeCell ref="F15:G16"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="F30:G32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="B76:C77"/>
-    <mergeCell ref="B78:C79"/>
-    <mergeCell ref="B80:C81"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="B84:C85"/>
-    <mergeCell ref="B86:C87"/>
-    <mergeCell ref="B88:C89"/>
-    <mergeCell ref="B90:C91"/>
-    <mergeCell ref="B92:C93"/>
-    <mergeCell ref="B82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="B97:C98"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="B99:C100"/>
-    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="B111:C112"/>
+    <mergeCell ref="D111:D112"/>
+    <mergeCell ref="B113:C114"/>
+    <mergeCell ref="D113:D114"/>
+    <mergeCell ref="B115:C116"/>
+    <mergeCell ref="D115:D116"/>
+    <mergeCell ref="B101:C102"/>
+    <mergeCell ref="D101:D102"/>
+    <mergeCell ref="B103:C104"/>
+    <mergeCell ref="D103:D104"/>
+    <mergeCell ref="B105:C106"/>
+    <mergeCell ref="D105:D106"/>
+    <mergeCell ref="B107:C108"/>
+    <mergeCell ref="D107:D108"/>
+    <mergeCell ref="B109:C110"/>
+    <mergeCell ref="D109:D110"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12531,7 +12992,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF77E60-696A-409F-8CE5-60C30FBE2FF1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Documents/Original/FlexChroma_Brim_info.xlsx
+++ b/Documents/Original/FlexChroma_Brim_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FlexChroma\Documents\Original\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j0814240\Documents\F-C\Git\FlexChroma\Documents\Original\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D40808-43E0-4FF5-990A-526EED5D3FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0FB0E0-3E7C-4397-927F-D3B576B0EB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7185" yWindow="8340" windowWidth="21585" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Brim" sheetId="13" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="128">
   <si>
     <t>Line</t>
     <phoneticPr fontId="1"/>
@@ -534,10 +534,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Prec</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Hint</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1890,40 +1886,235 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="77" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="62" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="65" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="66" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="71" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="72" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="70" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="69" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="89" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="95" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="96" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="91" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="88" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="94" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="92" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="93" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="85" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="90" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="61" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="75" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="86" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="87" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="60" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="57" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="73" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="82" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="83" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="84" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1953,136 +2144,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="70" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="62" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="65" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="66" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="71" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="72" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="69" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="57" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="77" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="76" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="80" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="57" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2103,112 +2189,22 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="73" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="75" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="60" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="73" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="82" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="83" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="76" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="80" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="61" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="85" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="86" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="87" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="88" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="89" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="90" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="91" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="92" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="93" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="94" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="95" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="96" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="84" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2444,23 +2440,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>365760</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>131</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="10" name="グループ化 9">
+        <xdr:cNvPr id="11" name="グループ化 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73AFDB20-4443-B1CD-A84A-76A0FF230175}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39123C91-C82C-5C4C-5242-543CF99DB5B5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2468,18 +2464,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6225540" y="12793980"/>
-          <a:ext cx="4739640" cy="2712720"/>
-          <a:chOff x="6225540" y="12793980"/>
-          <a:chExt cx="4739640" cy="2712720"/>
+          <a:off x="5657850" y="11553825"/>
+          <a:ext cx="5705475" cy="2714625"/>
+          <a:chOff x="5657850" y="11553825"/>
+          <a:chExt cx="5705475" cy="2714625"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="7" name="図 6">
+          <xdr:cNvPr id="6" name="図 5">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2499DB3-8C2E-3AA8-AC89-6205ACE43E12}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18643D00-2CB3-24AB-4C62-4D2ECABFCBA2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2502,8 +2498,8 @@
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="8823960" y="12793980"/>
-            <a:ext cx="2141220" cy="2712720"/>
+            <a:off x="5657850" y="11553825"/>
+            <a:ext cx="2809875" cy="1114425"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2522,10 +2518,10 @@
       </xdr:pic>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="9" name="図 8">
+          <xdr:cNvPr id="8" name="図 7">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{279D2115-7C27-10E6-7E39-F64261D1F9CB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DF0AD64-6F05-5A12-B50C-ADAAF719D2F1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2548,8 +2544,8 @@
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="6225540" y="12793980"/>
-            <a:ext cx="2529840" cy="1112520"/>
+            <a:off x="8553450" y="11553825"/>
+            <a:ext cx="2809875" cy="2714625"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2567,6 +2563,67 @@
         </xdr:spPr>
       </xdr:pic>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{254CF497-8889-5767-C0BE-812094C19D5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9258300" y="1876425"/>
+          <a:ext cx="6200775" cy="2390775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2661,8 +2718,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4598504" y="6722165"/>
-          <a:ext cx="5467764" cy="1773308"/>
+          <a:off x="5102087" y="6891130"/>
+          <a:ext cx="6069081" cy="1818034"/>
           <a:chOff x="4240696" y="5938629"/>
           <a:chExt cx="6069081" cy="1818034"/>
         </a:xfrm>
@@ -2834,8 +2891,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2946243" y="9442529"/>
-          <a:ext cx="5381092" cy="2457508"/>
+          <a:off x="3260982" y="9679411"/>
+          <a:ext cx="5957562" cy="2522113"/>
           <a:chOff x="3260982" y="9679411"/>
           <a:chExt cx="5957562" cy="2522113"/>
         </a:xfrm>
@@ -2966,8 +3023,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1362693" y="1401535"/>
-          <a:ext cx="10004714" cy="3417632"/>
+          <a:off x="1504207" y="1510392"/>
+          <a:ext cx="11136829" cy="3703382"/>
           <a:chOff x="1504207" y="1551214"/>
           <a:chExt cx="11136829" cy="3703382"/>
         </a:xfrm>
@@ -8547,20 +8604,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64526695-9BCB-44A9-9A34-911DAE368A41}">
   <dimension ref="A1:H184"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.21875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="2.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.125" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8570,7 +8627,7 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -8582,499 +8639,499 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="18" t="s">
+      <c r="B3" s="81"/>
+      <c r="C3" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="18" t="s">
+      <c r="D3" s="84"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="24"/>
+      <c r="G3" s="89"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="25"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="60"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="29" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="53" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="38"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="45"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="30" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="30" t="s">
+      <c r="D7" s="22"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="45" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="73"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="29" t="s">
+      <c r="E9" s="18"/>
+      <c r="F9" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="53" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="38"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="45"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="30" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="30" t="s">
+      <c r="E11" s="19"/>
+      <c r="F11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="45" t="s">
         <v>126</v>
       </c>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="73"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2"/>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="43" t="s">
+      <c r="E13" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="53" t="s">
         <v>12</v>
       </c>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="38"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="45"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="30" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="42" t="s">
+      <c r="D15" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="30" t="s">
+      <c r="F15" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="38" t="s">
+      <c r="G15" s="45" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="73"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2"/>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="50" t="s">
+      <c r="C17" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="21"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="G17" s="51"/>
+      <c r="G17" s="11"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="53"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="13"/>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="30" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="54" t="s">
+      <c r="D19" s="22"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="55"/>
+      <c r="G19" s="15"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="57"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2"/>
-      <c r="B21" s="59" t="s">
+      <c r="B21" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="60" t="s">
+      <c r="C21" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="61" t="s">
+      <c r="D21" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="35"/>
-      <c r="F21" s="60" t="s">
+      <c r="E21" s="19"/>
+      <c r="F21" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="G21" s="53" t="s">
+      <c r="G21" s="13" t="s">
         <v>12</v>
       </c>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="38"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="45"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="30" t="s">
+      <c r="B23" s="5"/>
+      <c r="C23" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="35"/>
-      <c r="F23" s="30" t="s">
+      <c r="E23" s="19"/>
+      <c r="F23" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="38" t="s">
+      <c r="G23" s="45" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="73"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2"/>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="D25" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="E25" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G25" s="37" t="s">
+      <c r="G25" s="53" t="s">
         <v>12</v>
       </c>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="38"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="45"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="30" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="44" t="s">
+      <c r="E27" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="30" t="s">
+      <c r="F27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="38" t="s">
+      <c r="G27" s="45" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="2"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="78"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="73"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="2"/>
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D29" s="41" t="s">
+      <c r="D29" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="43" t="s">
+      <c r="E29" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="29" t="s">
+      <c r="F29" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G29" s="37" t="s">
+      <c r="G29" s="53" t="s">
         <v>12</v>
       </c>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="38"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="45"/>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="2"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="30" t="s">
+      <c r="B31" s="5"/>
+      <c r="C31" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="42" t="s">
+      <c r="D31" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="E31" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="30" t="s">
+      <c r="F31" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G31" s="38" t="s">
+      <c r="G31" s="45" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="73"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2"/>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="41" t="s">
+      <c r="D33" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="43" t="s">
+      <c r="E33" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="F33" s="29" t="s">
+      <c r="F33" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G33" s="37" t="s">
+      <c r="G33" s="53" t="s">
         <v>12</v>
       </c>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="38"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="45"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="2"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="30" t="s">
+      <c r="B35" s="5"/>
+      <c r="C35" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="42" t="s">
+      <c r="D35" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="F35" s="30" t="s">
+      <c r="F35" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G35" s="38" t="s">
+      <c r="G35" s="45" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="66"/>
-      <c r="E36" s="91"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="67"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="46"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -9084,63 +9141,63 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="62" t="s">
+      <c r="C38" s="61" t="s">
         <v>35</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="62" t="s">
+      <c r="F38" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="G38" s="62"/>
+      <c r="G38" s="61"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="62"/>
+      <c r="C39" s="61"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="62"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
-      <c r="C40" s="62"/>
+      <c r="C40" s="61"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="62"/>
-      <c r="G40" s="62"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="62" t="s">
         <v>58</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="64"/>
+      <c r="F41" s="63"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="63"/>
+      <c r="C42" s="62"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="64"/>
+      <c r="F42" s="63"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -9150,7 +9207,7 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -9160,7 +9217,7 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -9170,295 +9227,295 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="2"/>
-      <c r="B46" s="100" t="s">
+      <c r="B46" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="65" t="s">
+      <c r="C46" s="72" t="s">
         <v>89</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="92" t="s">
+      <c r="G46" s="70" t="s">
         <v>50</v>
       </c>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2"/>
-      <c r="B47" s="101"/>
-      <c r="C47" s="40"/>
+      <c r="B47" s="65"/>
+      <c r="C47" s="73"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="39"/>
+      <c r="G47" s="71"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="2"/>
-      <c r="B48" s="102" t="s">
+      <c r="B48" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="38" t="s">
+      <c r="C48" s="45" t="s">
         <v>52</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="30" t="s">
+      <c r="G48" s="8" t="s">
         <v>37</v>
       </c>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="2"/>
-      <c r="B49" s="102"/>
-      <c r="C49" s="38"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="45"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="30"/>
+      <c r="G49" s="8"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="2"/>
-      <c r="B50" s="102" t="s">
+      <c r="B50" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="C50" s="38" t="s">
+      <c r="C50" s="45" t="s">
         <v>73</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="30" t="s">
+      <c r="G50" s="8" t="s">
         <v>74</v>
       </c>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="2"/>
-      <c r="B51" s="102"/>
-      <c r="C51" s="38"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="45"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="30"/>
+      <c r="G51" s="8"/>
       <c r="H51" s="2"/>
     </row>
-    <row r="52" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2"/>
-      <c r="B52" s="102" t="s">
+      <c r="B52" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="C52" s="38" t="s">
+      <c r="C52" s="45" t="s">
         <v>72</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="30" t="s">
+      <c r="G52" s="8" t="s">
         <v>71</v>
       </c>
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2"/>
-      <c r="B53" s="102"/>
-      <c r="C53" s="38"/>
+      <c r="B53" s="47"/>
+      <c r="C53" s="45"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
-      <c r="G53" s="30"/>
+      <c r="G53" s="8"/>
       <c r="H53" s="2"/>
     </row>
-    <row r="54" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="2"/>
-      <c r="B54" s="103" t="s">
+      <c r="B54" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C54" s="53" t="s">
+      <c r="C54" s="13" t="s">
         <v>51</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="60" t="s">
+      <c r="G54" s="54" t="s">
         <v>40</v>
       </c>
       <c r="H54" s="2"/>
     </row>
-    <row r="55" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="2"/>
-      <c r="B55" s="102"/>
-      <c r="C55" s="38"/>
+      <c r="B55" s="47"/>
+      <c r="C55" s="45"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="30"/>
+      <c r="G55" s="8"/>
       <c r="H55" s="2"/>
     </row>
-    <row r="56" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="2"/>
-      <c r="B56" s="97" t="s">
+      <c r="B56" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="C56" s="55" t="s">
+      <c r="C56" s="15" t="s">
         <v>53</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
-      <c r="G56" s="96" t="s">
+      <c r="G56" s="55" t="s">
         <v>41</v>
       </c>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="2"/>
-      <c r="B57" s="103"/>
-      <c r="C57" s="53"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="13"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
-      <c r="G57" s="60"/>
+      <c r="G57" s="54"/>
       <c r="H57" s="2"/>
     </row>
-    <row r="58" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="2"/>
-      <c r="B58" s="104" t="s">
+      <c r="B58" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="75" t="s">
+      <c r="C58" s="59" t="s">
         <v>54</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
-      <c r="G58" s="93" t="s">
+      <c r="G58" s="57" t="s">
         <v>39</v>
       </c>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="2"/>
-      <c r="B59" s="105"/>
-      <c r="C59" s="25"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="60"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
-      <c r="G59" s="94"/>
+      <c r="G59" s="58"/>
       <c r="H59" s="2"/>
     </row>
-    <row r="60" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="2"/>
-      <c r="B60" s="106" t="s">
+      <c r="B60" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="C60" s="99" t="s">
+      <c r="C60" s="52" t="s">
         <v>55</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
-      <c r="G60" s="95" t="s">
+      <c r="G60" s="51" t="s">
         <v>42</v>
       </c>
       <c r="H60" s="2"/>
     </row>
-    <row r="61" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="2"/>
-      <c r="B61" s="107"/>
-      <c r="C61" s="37"/>
+      <c r="B61" s="50"/>
+      <c r="C61" s="53"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
-      <c r="G61" s="29"/>
+      <c r="G61" s="7"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="2"/>
-      <c r="B62" s="102" t="s">
+      <c r="B62" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C62" s="38" t="s">
+      <c r="C62" s="45" t="s">
         <v>56</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
-      <c r="G62" s="30" t="s">
+      <c r="G62" s="8" t="s">
         <v>46</v>
       </c>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="2"/>
-      <c r="B63" s="102"/>
-      <c r="C63" s="38"/>
+      <c r="B63" s="47"/>
+      <c r="C63" s="45"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
-      <c r="G63" s="30"/>
+      <c r="G63" s="8"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="2"/>
-      <c r="B64" s="102" t="s">
+      <c r="B64" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="C64" s="38" t="s">
+      <c r="C64" s="45" t="s">
         <v>57</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
-      <c r="G64" s="30" t="s">
+      <c r="G64" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="2"/>
-      <c r="B65" s="102"/>
-      <c r="C65" s="38"/>
+      <c r="B65" s="47"/>
+      <c r="C65" s="45"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
-      <c r="G65" s="30"/>
+      <c r="G65" s="8"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="2"/>
-      <c r="B66" s="102" t="s">
+      <c r="B66" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="C66" s="38" t="s">
+      <c r="C66" s="45" t="s">
         <v>54</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
-      <c r="G66" s="30" t="s">
+      <c r="G66" s="8" t="s">
         <v>39</v>
       </c>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="2"/>
-      <c r="B67" s="102"/>
-      <c r="C67" s="38"/>
+      <c r="B67" s="47"/>
+      <c r="C67" s="45"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
-      <c r="G67" s="30"/>
+      <c r="G67" s="8"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="2"/>
-      <c r="B68" s="102" t="s">
+      <c r="B68" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="C68" s="38" t="s">
+      <c r="C68" s="45" t="s">
         <v>48</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
-      <c r="G68" s="30" t="s">
+      <c r="G68" s="8" t="s">
         <v>49</v>
       </c>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
-      <c r="B69" s="108"/>
-      <c r="C69" s="67"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="46"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
-      <c r="G69" s="49"/>
+      <c r="G69" s="9"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -9468,7 +9525,7 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -9478,12 +9535,12 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="2"/>
-      <c r="B72" s="77" t="s">
+      <c r="B72" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="C72" s="79" t="s">
+      <c r="C72" s="32" t="s">
         <v>89</v>
       </c>
       <c r="D72" s="2"/>
@@ -9492,22 +9549,22 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2"/>
-      <c r="B73" s="78"/>
-      <c r="C73" s="80"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="33"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2"/>
-      <c r="B74" s="81" t="s">
+      <c r="B74" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C74" s="82" t="s">
+      <c r="C74" s="34" t="s">
         <v>64</v>
       </c>
       <c r="D74" s="2"/>
@@ -9516,22 +9573,22 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="2"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="6"/>
+      <c r="B75" s="38"/>
+      <c r="C75" s="29"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2"/>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="29">
         <v>1</v>
       </c>
       <c r="D76" s="2"/>
@@ -9540,22 +9597,22 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="6"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="29"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2"/>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78" s="29">
         <v>2</v>
       </c>
       <c r="D78" s="2"/>
@@ -9564,22 +9621,22 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
     </row>
-    <row r="79" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="6"/>
+      <c r="B79" s="38"/>
+      <c r="C79" s="29"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
     </row>
-    <row r="80" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2"/>
-      <c r="B80" s="78" t="s">
+      <c r="B80" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C80" s="80">
+      <c r="C80" s="33">
         <v>4</v>
       </c>
       <c r="D80" s="2"/>
@@ -9588,17 +9645,17 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
     </row>
-    <row r="81" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
-      <c r="B81" s="83"/>
-      <c r="C81" s="84"/>
+      <c r="B81" s="43"/>
+      <c r="C81" s="44"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
     </row>
-    <row r="82" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -9608,7 +9665,7 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2" t="s">
         <v>95</v>
@@ -9620,12 +9677,12 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="2"/>
-      <c r="B84" s="77" t="s">
+      <c r="B84" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="C84" s="79" t="s">
+      <c r="C84" s="32" t="s">
         <v>89</v>
       </c>
       <c r="D84" s="2"/>
@@ -9634,22 +9691,22 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="2"/>
-      <c r="B85" s="78"/>
-      <c r="C85" s="80"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="33"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2"/>
-      <c r="B86" s="81" t="s">
+      <c r="B86" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="C86" s="82" t="s">
+      <c r="C86" s="34" t="s">
         <v>28</v>
       </c>
       <c r="D86" s="2"/>
@@ -9658,22 +9715,22 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="2"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="6"/>
+      <c r="B87" s="38"/>
+      <c r="C87" s="29"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="2"/>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" s="29" t="s">
         <v>29</v>
       </c>
       <c r="D88" s="2"/>
@@ -9682,23 +9739,23 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
     </row>
-    <row r="89" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="2"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="6"/>
+      <c r="B89" s="38"/>
+      <c r="C89" s="29"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
     </row>
-    <row r="90" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="2"/>
-      <c r="B90" s="97" t="s">
+      <c r="B90" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C90" s="88" t="s">
-        <v>127</v>
+      <c r="C90" s="40" t="s">
+        <v>85</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
@@ -9706,22 +9763,22 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
     </row>
-    <row r="91" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
-      <c r="B91" s="98"/>
-      <c r="C91" s="89"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="41"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
     </row>
-    <row r="92" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="2"/>
-      <c r="B92" s="81" t="s">
+      <c r="B92" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="C92" s="90" t="s">
+      <c r="C92" s="42" t="s">
         <v>33</v>
       </c>
       <c r="D92" s="2"/>
@@ -9730,22 +9787,22 @@
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
     </row>
-    <row r="93" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="2"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="6"/>
+      <c r="B93" s="38"/>
+      <c r="C93" s="29"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
     </row>
-    <row r="94" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="2"/>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="C94" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D94" s="2"/>
@@ -9754,22 +9811,22 @@
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
     </row>
-    <row r="95" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="2"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="6"/>
+      <c r="B95" s="38"/>
+      <c r="C95" s="29"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
     </row>
-    <row r="96" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="2"/>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="29" t="s">
         <v>30</v>
       </c>
       <c r="D96" s="2"/>
@@ -9778,22 +9835,22 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="2"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="6"/>
+      <c r="B97" s="38"/>
+      <c r="C97" s="29"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
     </row>
-    <row r="98" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="2"/>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="C98" s="6" t="s">
+      <c r="C98" s="29" t="s">
         <v>77</v>
       </c>
       <c r="D98" s="2"/>
@@ -9802,22 +9859,22 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="2"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="6"/>
+      <c r="B99" s="38"/>
+      <c r="C99" s="29"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="2"/>
-      <c r="B100" s="97" t="s">
+      <c r="B100" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C100" s="88" t="s">
+      <c r="C100" s="40" t="s">
         <v>79</v>
       </c>
       <c r="D100" s="2"/>
@@ -9826,17 +9883,17 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
-      <c r="B101" s="98"/>
-      <c r="C101" s="89"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="41"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -9846,7 +9903,7 @@
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -9856,12 +9913,12 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="2"/>
-      <c r="B104" s="77" t="s">
+      <c r="B104" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="C104" s="79" t="s">
+      <c r="C104" s="32" t="s">
         <v>89</v>
       </c>
       <c r="D104" s="2"/>
@@ -9870,22 +9927,22 @@
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="2"/>
-      <c r="B105" s="78"/>
-      <c r="C105" s="80"/>
+      <c r="B105" s="36"/>
+      <c r="C105" s="33"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="2"/>
-      <c r="B106" s="81" t="s">
+      <c r="B106" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="C106" s="82" t="s">
+      <c r="C106" s="34" t="s">
         <v>123</v>
       </c>
       <c r="D106" s="2"/>
@@ -9894,22 +9951,22 @@
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="2"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="6"/>
+      <c r="B107" s="38"/>
+      <c r="C107" s="29"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="2"/>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C108" s="29" t="s">
         <v>124</v>
       </c>
       <c r="D108" s="2"/>
@@ -9918,17 +9975,17 @@
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
     </row>
-    <row r="109" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="9"/>
+      <c r="B109" s="39"/>
+      <c r="C109" s="31"/>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
     </row>
-    <row r="110" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -9938,7 +9995,7 @@
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
     </row>
-    <row r="111" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -9948,7 +10005,7 @@
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
     </row>
-    <row r="112" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="2" t="s">
         <v>99</v>
@@ -9960,12 +10017,12 @@
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
     </row>
-    <row r="113" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="2"/>
-      <c r="B113" s="110" t="s">
+      <c r="B113" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="C113" s="79" t="s">
+      <c r="C113" s="32" t="s">
         <v>89</v>
       </c>
       <c r="E113" s="2"/>
@@ -9973,21 +10030,21 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="2"/>
-      <c r="B114" s="105"/>
-      <c r="C114" s="80"/>
+      <c r="B114" s="28"/>
+      <c r="C114" s="33"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="2"/>
-      <c r="B115" s="109" t="s">
+      <c r="B115" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="C115" s="82" t="s">
+      <c r="C115" s="34" t="s">
         <v>109</v>
       </c>
       <c r="E115" s="2"/>
@@ -9995,21 +10052,21 @@
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="2"/>
-      <c r="B116" s="103"/>
-      <c r="C116" s="6"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="29"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
     </row>
-    <row r="117" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="2"/>
-      <c r="B117" s="97" t="s">
+      <c r="B117" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="C117" s="6" t="s">
+      <c r="C117" s="29" t="s">
         <v>111</v>
       </c>
       <c r="E117" s="2"/>
@@ -10017,21 +10074,21 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="2"/>
-      <c r="B118" s="103"/>
-      <c r="C118" s="6"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="29"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="2"/>
-      <c r="B119" s="97" t="s">
+      <c r="B119" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C119" s="29" t="s">
         <v>110</v>
       </c>
       <c r="E119" s="2"/>
@@ -10039,21 +10096,21 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="2"/>
-      <c r="B120" s="103"/>
-      <c r="C120" s="6"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="29"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="2"/>
-      <c r="B121" s="97" t="s">
+      <c r="B121" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="C121" s="6" t="s">
+      <c r="C121" s="29" t="s">
         <v>112</v>
       </c>
       <c r="E121" s="2"/>
@@ -10061,21 +10118,21 @@
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="2"/>
-      <c r="B122" s="103"/>
-      <c r="C122" s="6"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="29"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="2"/>
-      <c r="B123" s="97" t="s">
+      <c r="B123" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C123" s="6" t="s">
+      <c r="C123" s="29" t="s">
         <v>113</v>
       </c>
       <c r="E123" s="2"/>
@@ -10083,21 +10140,21 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="2"/>
-      <c r="B124" s="103"/>
-      <c r="C124" s="6"/>
+      <c r="B124" s="25"/>
+      <c r="C124" s="29"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="2"/>
-      <c r="B125" s="97" t="s">
+      <c r="B125" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C125" s="6" t="s">
+      <c r="C125" s="29" t="s">
         <v>114</v>
       </c>
       <c r="E125" s="2"/>
@@ -10105,21 +10162,21 @@
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="2"/>
-      <c r="B126" s="103"/>
-      <c r="C126" s="6"/>
+      <c r="B126" s="25"/>
+      <c r="C126" s="29"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="2"/>
-      <c r="B127" s="97" t="s">
+      <c r="B127" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C127" s="6" t="s">
+      <c r="C127" s="29" t="s">
         <v>115</v>
       </c>
       <c r="E127" s="2"/>
@@ -10127,21 +10184,21 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="2"/>
-      <c r="B128" s="103"/>
-      <c r="C128" s="6"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="29"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="2"/>
-      <c r="B129" s="97" t="s">
+      <c r="B129" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C129" s="6" t="s">
+      <c r="C129" s="29" t="s">
         <v>116</v>
       </c>
       <c r="E129" s="2"/>
@@ -10149,21 +10206,21 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="2"/>
-      <c r="B130" s="103"/>
-      <c r="C130" s="6"/>
+      <c r="B130" s="25"/>
+      <c r="C130" s="29"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="2"/>
-      <c r="B131" s="97" t="s">
+      <c r="B131" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="C131" s="6" t="s">
+      <c r="C131" s="29" t="s">
         <v>126</v>
       </c>
       <c r="E131" s="2"/>
@@ -10171,21 +10228,21 @@
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="2"/>
-      <c r="B132" s="103"/>
-      <c r="C132" s="6"/>
+      <c r="B132" s="25"/>
+      <c r="C132" s="29"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="2"/>
-      <c r="B133" s="97" t="s">
+      <c r="B133" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="C133" s="29" t="s">
         <v>117</v>
       </c>
       <c r="D133" s="2"/>
@@ -10194,17 +10251,17 @@
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
-      <c r="B134" s="98"/>
-      <c r="C134" s="9"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="31"/>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -10214,7 +10271,7 @@
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -10224,7 +10281,7 @@
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -10234,7 +10291,7 @@
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -10244,7 +10301,7 @@
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -10254,7 +10311,7 @@
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
     </row>
-    <row r="140" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -10264,7 +10321,7 @@
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
     </row>
-    <row r="141" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -10274,7 +10331,7 @@
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -10284,7 +10341,7 @@
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -10294,7 +10351,7 @@
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -10304,7 +10361,7 @@
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -10314,7 +10371,7 @@
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -10324,7 +10381,7 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -10334,7 +10391,7 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -10344,7 +10401,7 @@
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -10354,7 +10411,7 @@
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -10364,7 +10421,7 @@
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -10374,7 +10431,7 @@
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -10384,7 +10441,7 @@
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
     </row>
-    <row r="153" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -10394,7 +10451,7 @@
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
     </row>
-    <row r="154" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -10404,7 +10461,7 @@
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
     </row>
-    <row r="155" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -10414,7 +10471,7 @@
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
     </row>
-    <row r="156" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -10424,7 +10481,7 @@
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
     </row>
-    <row r="157" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -10434,7 +10491,7 @@
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
     </row>
-    <row r="158" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -10444,7 +10501,7 @@
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
     </row>
-    <row r="159" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -10454,7 +10511,7 @@
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
     </row>
-    <row r="160" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -10464,7 +10521,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -10474,7 +10531,7 @@
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
     </row>
-    <row r="162" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -10484,7 +10541,7 @@
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
     </row>
-    <row r="163" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -10494,7 +10551,7 @@
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
     </row>
-    <row r="164" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -10504,7 +10561,7 @@
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
     </row>
-    <row r="165" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -10514,7 +10571,7 @@
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -10524,7 +10581,7 @@
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -10534,7 +10591,7 @@
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -10544,7 +10601,7 @@
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -10554,7 +10611,7 @@
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -10564,7 +10621,7 @@
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -10574,7 +10631,7 @@
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
     </row>
-    <row r="172" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -10584,7 +10641,7 @@
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
     </row>
-    <row r="173" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -10594,7 +10651,7 @@
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
     </row>
-    <row r="174" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -10604,7 +10661,7 @@
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
     </row>
-    <row r="175" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -10614,7 +10671,7 @@
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
     </row>
-    <row r="176" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -10624,7 +10681,7 @@
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
     </row>
-    <row r="177" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -10634,7 +10691,7 @@
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
     </row>
-    <row r="178" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -10644,7 +10701,7 @@
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
     </row>
-    <row r="179" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -10654,7 +10711,7 @@
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
     </row>
-    <row r="180" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -10664,130 +10721,57 @@
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
     </row>
-    <row r="181" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="2"/>
     </row>
-    <row r="182" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="2"/>
     </row>
-    <row r="183" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="F17:G18"/>
-    <mergeCell ref="F19:G20"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="D17:D20"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="B131:B132"/>
-    <mergeCell ref="C131:C132"/>
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="C125:C126"/>
-    <mergeCell ref="C127:C128"/>
-    <mergeCell ref="C129:C130"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="B129:B130"/>
-    <mergeCell ref="B127:B128"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="C115:C116"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="F38:G40"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:E4"/>
+    <mergeCell ref="F3:G4"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="B29:B32"/>
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="D29:D30"/>
@@ -10812,47 +10796,120 @@
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="B21:B24"/>
     <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:E4"/>
-    <mergeCell ref="F3:G4"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="F38:G40"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="C131:C132"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="C125:C126"/>
+    <mergeCell ref="C127:C128"/>
+    <mergeCell ref="C129:C130"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="B127:B128"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="F17:G18"/>
+    <mergeCell ref="F19:G20"/>
+    <mergeCell ref="E17:E20"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="C115:C116"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="B90:B91"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10864,18 +10921,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D09D71-3F9C-4BDB-BCC5-2D63E9BEF5B5}">
   <dimension ref="A1:H174"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
     <col min="2" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="2.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.375" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.125" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10885,7 +10942,7 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -10897,383 +10954,383 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="18" t="s">
+      <c r="B3" s="81"/>
+      <c r="C3" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="18" t="s">
+      <c r="D3" s="84"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="24"/>
+      <c r="G3" s="89"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="25"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="60"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="29" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="53" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="38"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="45"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="30" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="30" t="s">
+      <c r="D7" s="22"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="45" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="73"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="53" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="38"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="45"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="30" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="45" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="73"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2"/>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="50" t="s">
+      <c r="D13" s="21"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G13" s="51"/>
+      <c r="G13" s="11"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="53"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="13"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="30" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="54" t="s">
+      <c r="D15" s="22"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="G15" s="55"/>
+      <c r="G15" s="15"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="57"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2"/>
-      <c r="B17" s="59" t="s">
+      <c r="B17" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="60" t="s">
+      <c r="C17" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="61" t="s">
+      <c r="D17" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="61" t="s">
+      <c r="E17" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="60" t="s">
+      <c r="F17" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="G17" s="53" t="s">
+      <c r="G17" s="13" t="s">
         <v>12</v>
       </c>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="38"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="45"/>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="30" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D19" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="F19" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="45" t="s">
         <v>81</v>
       </c>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="73"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2"/>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="D21" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G21" s="37" t="s">
+      <c r="G21" s="53" t="s">
         <v>12</v>
       </c>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="38"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="45"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="30" t="s">
+      <c r="B23" s="5"/>
+      <c r="C23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="E23" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="F23" s="30" t="s">
+      <c r="F23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="G23" s="38" t="s">
+      <c r="G23" s="45" t="s">
         <v>81</v>
       </c>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="73"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2"/>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="D25" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="41" t="s">
+      <c r="E25" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G25" s="37" t="s">
+      <c r="G25" s="53" t="s">
         <v>12</v>
       </c>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="38"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="45"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="30" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="E27" s="42" t="s">
+      <c r="E27" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="30" t="s">
+      <c r="F27" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="G27" s="38" t="s">
+      <c r="G27" s="45" t="s">
         <v>81</v>
       </c>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="67"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="46"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -11283,57 +11340,57 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="62"/>
+      <c r="C30" s="61"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="62"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="62"/>
+      <c r="C31" s="61"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="62"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="62"/>
+      <c r="C32" s="61"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="62"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="63"/>
+      <c r="C33" s="62"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="64"/>
+      <c r="F33" s="63"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="63"/>
+      <c r="C34" s="62"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="64"/>
+      <c r="F34" s="63"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -11343,7 +11400,7 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -11353,7 +11410,7 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
         <v>96</v>
@@ -11367,64 +11424,64 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2"/>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="65" t="s">
+      <c r="C38" s="72" t="s">
         <v>89</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="108" t="s">
         <v>97</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="40"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="73"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="14"/>
+      <c r="E39" s="106"/>
+      <c r="F39" s="109"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="2"/>
-      <c r="B40" s="68" t="s">
+      <c r="B40" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="C40" s="38" t="s">
+      <c r="C40" s="45" t="s">
         <v>52</v>
       </c>
       <c r="D40" s="2"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="14"/>
+      <c r="E40" s="106"/>
+      <c r="F40" s="109"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="38"/>
+      <c r="B41" s="97"/>
+      <c r="C41" s="45"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="15"/>
+      <c r="E41" s="107"/>
+      <c r="F41" s="110"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="2"/>
-      <c r="B42" s="68" t="s">
+      <c r="B42" s="97" t="s">
         <v>74</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C42" s="45" t="s">
         <v>73</v>
       </c>
       <c r="D42" s="2"/>
@@ -11432,22 +11489,22 @@
       <c r="F42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="38"/>
+      <c r="B43" s="97"/>
+      <c r="C43" s="45"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="2"/>
-      <c r="B44" s="68" t="s">
+      <c r="B44" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="C44" s="38" t="s">
+      <c r="C44" s="45" t="s">
         <v>72</v>
       </c>
       <c r="D44" s="2"/>
@@ -11456,22 +11513,22 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="2"/>
-      <c r="B45" s="68"/>
-      <c r="C45" s="38"/>
+      <c r="B45" s="97"/>
+      <c r="C45" s="45"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="2"/>
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="C46" s="53" t="s">
+      <c r="C46" s="13" t="s">
         <v>51</v>
       </c>
       <c r="D46" s="2"/>
@@ -11480,22 +11537,22 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2"/>
-      <c r="B47" s="68"/>
-      <c r="C47" s="38"/>
+      <c r="B47" s="97"/>
+      <c r="C47" s="45"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="2"/>
-      <c r="B48" s="72" t="s">
+      <c r="B48" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="55" t="s">
+      <c r="C48" s="15" t="s">
         <v>53</v>
       </c>
       <c r="D48" s="2"/>
@@ -11504,22 +11561,22 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="2"/>
-      <c r="B49" s="69"/>
-      <c r="C49" s="53"/>
+      <c r="B49" s="99"/>
+      <c r="C49" s="13"/>
       <c r="D49" s="3"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="2"/>
-      <c r="B50" s="73" t="s">
+      <c r="B50" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="75" t="s">
+      <c r="C50" s="59" t="s">
         <v>54</v>
       </c>
       <c r="D50" s="2"/>
@@ -11528,22 +11585,22 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
-      <c r="B51" s="74"/>
-      <c r="C51" s="57"/>
+      <c r="B51" s="104"/>
+      <c r="C51" s="17"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
     </row>
-    <row r="52" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2"/>
-      <c r="B52" s="70" t="s">
+      <c r="B52" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="25" t="s">
+      <c r="C52" s="60" t="s">
         <v>55</v>
       </c>
       <c r="D52" s="2"/>
@@ -11552,22 +11609,22 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2"/>
-      <c r="B53" s="71"/>
-      <c r="C53" s="37"/>
+      <c r="B53" s="101"/>
+      <c r="C53" s="53"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
     </row>
-    <row r="54" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="2"/>
-      <c r="B54" s="68" t="s">
+      <c r="B54" s="97" t="s">
         <v>43</v>
       </c>
-      <c r="C54" s="38" t="s">
+      <c r="C54" s="45" t="s">
         <v>56</v>
       </c>
       <c r="D54" s="2"/>
@@ -11576,22 +11633,22 @@
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
     </row>
-    <row r="55" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="2"/>
-      <c r="B55" s="68"/>
-      <c r="C55" s="38"/>
+      <c r="B55" s="97"/>
+      <c r="C55" s="45"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
     </row>
-    <row r="56" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="2"/>
-      <c r="B56" s="68" t="s">
+      <c r="B56" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="38" t="s">
+      <c r="C56" s="45" t="s">
         <v>57</v>
       </c>
       <c r="D56" s="2"/>
@@ -11600,22 +11657,22 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="2"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="38"/>
+      <c r="B57" s="97"/>
+      <c r="C57" s="45"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
     </row>
-    <row r="58" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="2"/>
-      <c r="B58" s="68" t="s">
+      <c r="B58" s="97" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="38" t="s">
+      <c r="C58" s="45" t="s">
         <v>54</v>
       </c>
       <c r="D58" s="2"/>
@@ -11624,22 +11681,22 @@
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="2"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="38"/>
+      <c r="B59" s="97"/>
+      <c r="C59" s="45"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
     </row>
-    <row r="60" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="2"/>
-      <c r="B60" s="68" t="s">
+      <c r="B60" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="38" t="s">
+      <c r="C60" s="45" t="s">
         <v>48</v>
       </c>
       <c r="D60" s="2"/>
@@ -11648,17 +11705,17 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
     </row>
-    <row r="61" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
-      <c r="B61" s="76"/>
-      <c r="C61" s="67"/>
+      <c r="B61" s="98"/>
+      <c r="C61" s="46"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -11668,7 +11725,7 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
         <v>88</v>
@@ -11680,12 +11737,12 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="2"/>
-      <c r="B64" s="77" t="s">
+      <c r="B64" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="C64" s="79" t="s">
+      <c r="C64" s="32" t="s">
         <v>89</v>
       </c>
       <c r="D64" s="2"/>
@@ -11694,22 +11751,22 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="2"/>
-      <c r="B65" s="78"/>
-      <c r="C65" s="80"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="33"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="2"/>
-      <c r="B66" s="81" t="s">
+      <c r="B66" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C66" s="82" t="s">
+      <c r="C66" s="34" t="s">
         <v>86</v>
       </c>
       <c r="D66" s="2"/>
@@ -11718,22 +11775,22 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="2"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="6"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="29"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="2"/>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="29" t="s">
         <v>87</v>
       </c>
       <c r="D68" s="2"/>
@@ -11742,22 +11799,22 @@
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="6"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="29"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2"/>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="29" t="s">
         <v>92</v>
       </c>
       <c r="D70" s="2"/>
@@ -11766,22 +11823,22 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="6"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="29"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="2"/>
-      <c r="B72" s="78" t="s">
+      <c r="B72" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C72" s="80" t="s">
+      <c r="C72" s="33" t="s">
         <v>93</v>
       </c>
       <c r="D72" s="2"/>
@@ -11790,17 +11847,17 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
-      <c r="B73" s="83"/>
-      <c r="C73" s="84"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="44"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -11810,7 +11867,7 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="2" t="s">
         <v>95</v>
@@ -11822,13 +11879,13 @@
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2"/>
-      <c r="B76" s="77" t="s">
+      <c r="B76" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="C76" s="85"/>
-      <c r="D76" s="79" t="s">
+      <c r="C76" s="94"/>
+      <c r="D76" s="32" t="s">
         <v>89</v>
       </c>
       <c r="E76" s="2"/>
@@ -11836,23 +11893,23 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2"/>
-      <c r="B77" s="78"/>
-      <c r="C77" s="86"/>
-      <c r="D77" s="80"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="95"/>
+      <c r="D77" s="33"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2"/>
-      <c r="B78" s="81" t="s">
+      <c r="B78" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C78" s="87"/>
-      <c r="D78" s="82" t="s">
+      <c r="C78" s="96"/>
+      <c r="D78" s="34" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="2"/>
@@ -11860,23 +11917,23 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
     </row>
-    <row r="79" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="6"/>
+      <c r="B79" s="38"/>
+      <c r="C79" s="92"/>
+      <c r="D79" s="29"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
     </row>
-    <row r="80" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2"/>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C80" s="5"/>
-      <c r="D80" s="6" t="s">
+      <c r="C80" s="92"/>
+      <c r="D80" s="29" t="s">
         <v>29</v>
       </c>
       <c r="E80" s="2"/>
@@ -11884,23 +11941,23 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
     </row>
-    <row r="81" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="2"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="6"/>
+      <c r="B81" s="38"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="29"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
     </row>
-    <row r="82" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="2"/>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="C82" s="5"/>
-      <c r="D82" s="6" t="s">
+      <c r="C82" s="92"/>
+      <c r="D82" s="29" t="s">
         <v>85</v>
       </c>
       <c r="E82" s="2"/>
@@ -11908,23 +11965,23 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="9"/>
+      <c r="B83" s="39"/>
+      <c r="C83" s="93"/>
+      <c r="D83" s="31"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="2"/>
-      <c r="B84" s="81" t="s">
+      <c r="B84" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C84" s="87"/>
-      <c r="D84" s="90" t="s">
+      <c r="C84" s="96"/>
+      <c r="D84" s="42" t="s">
         <v>33</v>
       </c>
       <c r="E84" s="2"/>
@@ -11932,23 +11989,23 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="2"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="6"/>
+      <c r="B85" s="38"/>
+      <c r="C85" s="92"/>
+      <c r="D85" s="29"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2"/>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C86" s="5"/>
-      <c r="D86" s="6" t="s">
+      <c r="C86" s="92"/>
+      <c r="D86" s="29" t="s">
         <v>34</v>
       </c>
       <c r="E86" s="2"/>
@@ -11956,23 +12013,23 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="2"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="6"/>
+      <c r="B87" s="38"/>
+      <c r="C87" s="92"/>
+      <c r="D87" s="29"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="2"/>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C88" s="5"/>
-      <c r="D88" s="6" t="s">
+      <c r="C88" s="92"/>
+      <c r="D88" s="29" t="s">
         <v>30</v>
       </c>
       <c r="E88" s="2"/>
@@ -11980,23 +12037,23 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
     </row>
-    <row r="89" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="2"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="6"/>
+      <c r="B89" s="38"/>
+      <c r="C89" s="92"/>
+      <c r="D89" s="29"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
     </row>
-    <row r="90" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="2"/>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C90" s="5"/>
-      <c r="D90" s="6" t="s">
+      <c r="C90" s="92"/>
+      <c r="D90" s="29" t="s">
         <v>77</v>
       </c>
       <c r="E90" s="2"/>
@@ -12004,35 +12061,35 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
     </row>
-    <row r="91" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="2"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="6"/>
+      <c r="B91" s="38"/>
+      <c r="C91" s="92"/>
+      <c r="D91" s="29"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
     </row>
-    <row r="92" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="2"/>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="5"/>
-      <c r="D92" s="88" t="s">
+      <c r="C92" s="92"/>
+      <c r="D92" s="40" t="s">
         <v>79</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
     </row>
-    <row r="93" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="89"/>
+      <c r="B93" s="39"/>
+      <c r="C93" s="93"/>
+      <c r="D93" s="41"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
     </row>
-    <row r="94" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -12040,7 +12097,7 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
     </row>
-    <row r="95" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -12048,7 +12105,7 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
     </row>
-    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2" t="s">
         <v>99</v>
@@ -12058,53 +12115,53 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
     </row>
-    <row r="97" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="2"/>
-      <c r="B97" s="77" t="s">
+      <c r="B97" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C97" s="85"/>
-      <c r="D97" s="79" t="s">
+      <c r="C97" s="94"/>
+      <c r="D97" s="32" t="s">
         <v>89</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
     </row>
-    <row r="98" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="2"/>
-      <c r="B98" s="78"/>
-      <c r="C98" s="86"/>
-      <c r="D98" s="80"/>
+      <c r="B98" s="36"/>
+      <c r="C98" s="95"/>
+      <c r="D98" s="33"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
     </row>
-    <row r="99" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="2"/>
-      <c r="B99" s="81" t="s">
+      <c r="B99" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="C99" s="87"/>
-      <c r="D99" s="82" t="s">
+      <c r="C99" s="96"/>
+      <c r="D99" s="34" t="s">
         <v>109</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
     </row>
-    <row r="100" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="2"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="5"/>
-      <c r="D100" s="6"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="92"/>
+      <c r="D100" s="29"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
     </row>
-    <row r="101" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="2"/>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="C101" s="5"/>
-      <c r="D101" s="6" t="s">
+      <c r="C101" s="92"/>
+      <c r="D101" s="29" t="s">
         <v>111</v>
       </c>
       <c r="E101" s="2"/>
@@ -12112,23 +12169,23 @@
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="2"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="5"/>
-      <c r="D102" s="6"/>
+      <c r="B102" s="38"/>
+      <c r="C102" s="92"/>
+      <c r="D102" s="29"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="2"/>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="5"/>
-      <c r="D103" s="6" t="s">
+      <c r="C103" s="92"/>
+      <c r="D103" s="29" t="s">
         <v>110</v>
       </c>
       <c r="E103" s="2"/>
@@ -12136,23 +12193,23 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="2"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="5"/>
-      <c r="D104" s="6"/>
+      <c r="B104" s="38"/>
+      <c r="C104" s="92"/>
+      <c r="D104" s="29"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="2"/>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="C105" s="5"/>
-      <c r="D105" s="6" t="s">
+      <c r="C105" s="92"/>
+      <c r="D105" s="29" t="s">
         <v>112</v>
       </c>
       <c r="E105" s="2"/>
@@ -12160,23 +12217,23 @@
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="2"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="6"/>
+      <c r="B106" s="38"/>
+      <c r="C106" s="92"/>
+      <c r="D106" s="29"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="2"/>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="C107" s="5"/>
-      <c r="D107" s="6" t="s">
+      <c r="C107" s="92"/>
+      <c r="D107" s="29" t="s">
         <v>113</v>
       </c>
       <c r="E107" s="2"/>
@@ -12184,23 +12241,23 @@
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="2"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="5"/>
-      <c r="D108" s="6"/>
+      <c r="B108" s="38"/>
+      <c r="C108" s="92"/>
+      <c r="D108" s="29"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
     </row>
-    <row r="109" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="2"/>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="C109" s="5"/>
-      <c r="D109" s="6" t="s">
+      <c r="C109" s="92"/>
+      <c r="D109" s="29" t="s">
         <v>114</v>
       </c>
       <c r="E109" s="2"/>
@@ -12208,23 +12265,23 @@
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
     </row>
-    <row r="110" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="2"/>
-      <c r="B110" s="4"/>
-      <c r="C110" s="5"/>
-      <c r="D110" s="6"/>
+      <c r="B110" s="38"/>
+      <c r="C110" s="92"/>
+      <c r="D110" s="29"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
     </row>
-    <row r="111" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="2"/>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="C111" s="5"/>
-      <c r="D111" s="6" t="s">
+      <c r="C111" s="92"/>
+      <c r="D111" s="29" t="s">
         <v>115</v>
       </c>
       <c r="E111" s="2"/>
@@ -12232,23 +12289,23 @@
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
     </row>
-    <row r="112" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="2"/>
-      <c r="B112" s="4"/>
-      <c r="C112" s="5"/>
-      <c r="D112" s="6"/>
+      <c r="B112" s="38"/>
+      <c r="C112" s="92"/>
+      <c r="D112" s="29"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
     </row>
-    <row r="113" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="2"/>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="C113" s="5"/>
-      <c r="D113" s="6" t="s">
+      <c r="C113" s="92"/>
+      <c r="D113" s="29" t="s">
         <v>116</v>
       </c>
       <c r="E113" s="2"/>
@@ -12256,23 +12313,23 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="2"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="5"/>
-      <c r="D114" s="6"/>
+      <c r="B114" s="38"/>
+      <c r="C114" s="92"/>
+      <c r="D114" s="29"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="2"/>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="C115" s="5"/>
-      <c r="D115" s="6" t="s">
+      <c r="C115" s="92"/>
+      <c r="D115" s="29" t="s">
         <v>117</v>
       </c>
       <c r="E115" s="2"/>
@@ -12280,17 +12337,17 @@
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
-      <c r="B116" s="7"/>
-      <c r="C116" s="8"/>
-      <c r="D116" s="9"/>
+      <c r="B116" s="39"/>
+      <c r="C116" s="93"/>
+      <c r="D116" s="31"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
     </row>
-    <row r="117" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -12300,7 +12357,7 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -12310,7 +12367,7 @@
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -12320,7 +12377,7 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -12330,7 +12387,7 @@
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -12340,7 +12397,7 @@
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -12350,7 +12407,7 @@
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -12360,7 +12417,7 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -12370,7 +12427,7 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -12380,7 +12437,7 @@
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -12390,7 +12447,7 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -12400,7 +12457,7 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -12410,7 +12467,7 @@
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -12420,7 +12477,7 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -12430,7 +12487,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -12440,7 +12497,7 @@
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -12450,7 +12507,7 @@
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -12460,7 +12517,7 @@
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -12470,7 +12527,7 @@
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -12480,7 +12537,7 @@
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -12490,7 +12547,7 @@
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -12500,7 +12557,7 @@
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -12510,7 +12567,7 @@
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -12520,7 +12577,7 @@
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
     </row>
-    <row r="140" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -12530,7 +12587,7 @@
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
     </row>
-    <row r="141" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -12540,7 +12597,7 @@
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -12550,7 +12607,7 @@
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -12560,7 +12617,7 @@
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -12570,7 +12627,7 @@
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -12580,7 +12637,7 @@
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -12590,7 +12647,7 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -12600,7 +12657,7 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -12610,7 +12667,7 @@
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -12620,7 +12677,7 @@
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -12630,7 +12687,7 @@
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -12640,7 +12697,7 @@
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -12650,7 +12707,7 @@
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
     </row>
-    <row r="153" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -12660,7 +12717,7 @@
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
     </row>
-    <row r="154" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -12670,7 +12727,7 @@
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
     </row>
-    <row r="155" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -12680,7 +12737,7 @@
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
     </row>
-    <row r="156" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -12690,7 +12747,7 @@
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
     </row>
-    <row r="157" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -12700,7 +12757,7 @@
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
     </row>
-    <row r="158" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -12710,7 +12767,7 @@
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
     </row>
-    <row r="159" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -12720,7 +12777,7 @@
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
     </row>
-    <row r="160" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -12730,7 +12787,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -12740,7 +12797,7 @@
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
     </row>
-    <row r="162" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -12750,7 +12807,7 @@
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
     </row>
-    <row r="163" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -12760,7 +12817,7 @@
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
     </row>
-    <row r="164" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -12770,7 +12827,7 @@
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
     </row>
-    <row r="165" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -12780,7 +12837,7 @@
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -12790,7 +12847,7 @@
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -12800,7 +12857,7 @@
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -12810,7 +12867,7 @@
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -12820,7 +12877,7 @@
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -12830,68 +12887,84 @@
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="2"/>
     </row>
-    <row r="172" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="2"/>
     </row>
-    <row r="173" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="141">
-    <mergeCell ref="B82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="B97:C98"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="B99:C100"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="B84:C85"/>
-    <mergeCell ref="B86:C87"/>
-    <mergeCell ref="B88:C89"/>
-    <mergeCell ref="B90:C91"/>
-    <mergeCell ref="B92:C93"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="B76:C77"/>
-    <mergeCell ref="B78:C79"/>
-    <mergeCell ref="B80:C81"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B115:C116"/>
+    <mergeCell ref="D115:D116"/>
+    <mergeCell ref="B101:C102"/>
+    <mergeCell ref="D101:D102"/>
+    <mergeCell ref="B103:C104"/>
+    <mergeCell ref="D103:D104"/>
+    <mergeCell ref="B105:C106"/>
+    <mergeCell ref="D105:D106"/>
+    <mergeCell ref="B107:C108"/>
+    <mergeCell ref="D107:D108"/>
+    <mergeCell ref="B109:C110"/>
+    <mergeCell ref="D109:D110"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="B111:C112"/>
+    <mergeCell ref="D111:D112"/>
+    <mergeCell ref="B113:C114"/>
+    <mergeCell ref="D113:D114"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:E4"/>
+    <mergeCell ref="F3:G4"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="E13:E16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="F13:G14"/>
+    <mergeCell ref="F15:G16"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
     <mergeCell ref="B38:B39"/>
     <mergeCell ref="C38:C39"/>
     <mergeCell ref="G25:G26"/>
@@ -12911,76 +12984,60 @@
     <mergeCell ref="F30:G32"/>
     <mergeCell ref="C33:C34"/>
     <mergeCell ref="F33:F34"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="E13:E16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="F13:G14"/>
-    <mergeCell ref="F15:G16"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
     <mergeCell ref="E38:E41"/>
     <mergeCell ref="F38:F41"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:E4"/>
-    <mergeCell ref="F3:G4"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="B111:C112"/>
-    <mergeCell ref="D111:D112"/>
-    <mergeCell ref="B113:C114"/>
-    <mergeCell ref="D113:D114"/>
-    <mergeCell ref="B115:C116"/>
-    <mergeCell ref="D115:D116"/>
-    <mergeCell ref="B101:C102"/>
-    <mergeCell ref="D101:D102"/>
-    <mergeCell ref="B103:C104"/>
-    <mergeCell ref="D103:D104"/>
-    <mergeCell ref="B105:C106"/>
-    <mergeCell ref="D105:D106"/>
-    <mergeCell ref="B107:C108"/>
-    <mergeCell ref="D107:D108"/>
-    <mergeCell ref="B109:C110"/>
-    <mergeCell ref="D109:D110"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="B76:C77"/>
+    <mergeCell ref="B78:C79"/>
+    <mergeCell ref="B80:C81"/>
+    <mergeCell ref="B82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="B97:C98"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="B99:C100"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="B84:C85"/>
+    <mergeCell ref="B86:C87"/>
+    <mergeCell ref="B88:C89"/>
+    <mergeCell ref="B90:C91"/>
+    <mergeCell ref="B92:C93"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12992,7 +13049,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF77E60-696A-409F-8CE5-60C30FBE2FF1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
